--- a/docs/templates/mapping模板.xlsx
+++ b/docs/templates/mapping模板.xlsx
@@ -1397,7 +1397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -2271,6 +2271,190 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>赋值</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>IF(t.status='已作废','Y','N')</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>del_flag</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>删除标识</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>nvarchar(1)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>审计字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>赋值</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>'${P_CYCLE_ID}'</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>crt_cycle_id</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>创建批次ID</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>审计字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>赋值</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>'${P_CYCLE_ID}'</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>last_upd_cycle_id</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>最后更新批次ID</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>审计字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>赋值</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>dw_last_update_date</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>数仓最后更新时间</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>timestamp(0) without time zone</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>审计字段</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/templates/mapping模板.xlsx
+++ b/docs/templates/mapping模板.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>dwl_con_pu_any_f</t>
+          <t>dwl_con_pu_any_i</t>
         </is>
       </c>
       <c r="K2" s="3" t="n"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>dwl_con_pu_any_f</t>
+          <t>dwl_con_pu_any_i</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>dwl_con_pu_any_f</t>
+          <t>dwl_con_pu_any_i</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>dwl_con_pu_any_f</t>
+          <t>dwl_con_pu_any_i</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2280,12 +2280,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -2326,12 +2320,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -2372,12 +2360,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -2418,12 +2400,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>赋值</t>

--- a/docs/templates/mapping模板.xlsx
+++ b/docs/templates/mapping模板.xlsx
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>源表物理表别名</t>
+          <t>源表别名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
